--- a/research/traditional_assets/database/data/austria/austria_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_chemical_basic.xlsx
@@ -588,49 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0213</v>
-      </c>
-      <c r="E2">
-        <v>-0.248</v>
-      </c>
-      <c r="F2">
-        <v>0.331</v>
+        <v>0.0206</v>
       </c>
       <c r="G2">
-        <v>0.1664159607315336</v>
+        <v>0.1027176416397973</v>
       </c>
       <c r="H2">
-        <v>0.1532341065632175</v>
+        <v>0.08959005066789499</v>
       </c>
       <c r="I2">
-        <v>0.04667088908241628</v>
+        <v>-0.04955473668048518</v>
       </c>
       <c r="J2">
-        <v>0.02333544454120814</v>
+        <v>-0.04955473668048518</v>
       </c>
       <c r="K2">
-        <v>66.3</v>
+        <v>-295.2</v>
       </c>
       <c r="L2">
-        <v>0.02624495289367429</v>
+        <v>-0.1133118378627361</v>
       </c>
       <c r="M2">
-        <v>141.4</v>
+        <v>30.5</v>
       </c>
       <c r="N2">
-        <v>0.09093832400797479</v>
+        <v>0.02009884678747941</v>
       </c>
       <c r="O2">
-        <v>2.132730015082956</v>
+        <v>-0.103319783197832</v>
       </c>
       <c r="P2">
-        <v>141.4</v>
+        <v>30.5</v>
       </c>
       <c r="Q2">
-        <v>0.09093832400797479</v>
+        <v>0.02009884678747941</v>
       </c>
       <c r="R2">
-        <v>2.132730015082956</v>
+        <v>-0.103319783197832</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,70 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>733.3</v>
+        <v>791.4</v>
       </c>
       <c r="V2">
-        <v>0.471605891054087</v>
+        <v>0.5215156507413509</v>
       </c>
       <c r="W2">
-        <v>0.02978838118344791</v>
+        <v>-0.1569294561692627</v>
       </c>
       <c r="X2">
-        <v>0.1818477236174779</v>
+        <v>0.147171209259801</v>
       </c>
       <c r="Y2">
-        <v>-0.15205934243403</v>
+        <v>-0.3041006654290636</v>
       </c>
       <c r="Z2">
-        <v>0.7953028585820426</v>
+        <v>0.7297070192146098</v>
       </c>
       <c r="AA2">
-        <v>0.01855874574990556</v>
+        <v>-0.03616043919108173</v>
       </c>
       <c r="AB2">
-        <v>0.09881400432582654</v>
+        <v>0.0806115332843247</v>
       </c>
       <c r="AC2">
-        <v>-0.08025525857592099</v>
+        <v>-0.1167719724754064</v>
       </c>
       <c r="AD2">
-        <v>2422.4</v>
+        <v>2613.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2422.4</v>
+        <v>2613.1</v>
       </c>
       <c r="AG2">
-        <v>1689.1</v>
+        <v>1821.7</v>
       </c>
       <c r="AH2">
-        <v>0.6090563950418626</v>
+        <v>0.6326199583595603</v>
       </c>
       <c r="AI2">
-        <v>0.5283545629035072</v>
+        <v>0.5202891048104492</v>
       </c>
       <c r="AJ2">
-        <v>0.5206843403205919</v>
+        <v>0.5455498322951605</v>
       </c>
       <c r="AK2">
-        <v>0.4385564065948332</v>
+        <v>0.4305601512644764</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>119.9</v>
       </c>
       <c r="AM2">
-        <v>-22.3</v>
+        <v>119.9</v>
       </c>
       <c r="AN2">
-        <v>8.074666666666667</v>
+        <v>14.14780725500812</v>
+      </c>
+      <c r="AO2">
+        <v>-1.0767306088407</v>
       </c>
       <c r="AP2">
-        <v>5.630333333333334</v>
+        <v>9.863021115322143</v>
       </c>
       <c r="AQ2">
-        <v>-5.286995515695067</v>
+        <v>-1.0767306088407</v>
       </c>
     </row>
     <row r="3">
@@ -722,49 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0213</v>
-      </c>
-      <c r="E3">
-        <v>-0.248</v>
-      </c>
-      <c r="F3">
-        <v>0.331</v>
+        <v>0.0206</v>
       </c>
       <c r="G3">
-        <v>0.1664159607315336</v>
+        <v>0.1027176416397973</v>
       </c>
       <c r="H3">
-        <v>0.1532341065632175</v>
+        <v>0.08959005066789499</v>
       </c>
       <c r="I3">
-        <v>0.04667088908241628</v>
+        <v>-0.04955473668048518</v>
       </c>
       <c r="J3">
-        <v>0.02333544454120814</v>
+        <v>-0.04955473668048518</v>
       </c>
       <c r="K3">
-        <v>66.3</v>
+        <v>-295.2</v>
       </c>
       <c r="L3">
-        <v>0.02624495289367429</v>
+        <v>-0.1133118378627361</v>
       </c>
       <c r="M3">
-        <v>141.4</v>
+        <v>30.5</v>
       </c>
       <c r="N3">
-        <v>0.09093832400797479</v>
+        <v>0.02009884678747941</v>
       </c>
       <c r="O3">
-        <v>2.132730015082956</v>
+        <v>-0.103319783197832</v>
       </c>
       <c r="P3">
-        <v>141.4</v>
+        <v>30.5</v>
       </c>
       <c r="Q3">
-        <v>0.09093832400797479</v>
+        <v>0.02009884678747941</v>
       </c>
       <c r="R3">
-        <v>2.132730015082956</v>
+        <v>-0.103319783197832</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,70 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>733.3</v>
+        <v>791.4</v>
       </c>
       <c r="V3">
-        <v>0.471605891054087</v>
+        <v>0.5215156507413509</v>
       </c>
       <c r="W3">
-        <v>0.02978838118344791</v>
+        <v>-0.1569294561692627</v>
       </c>
       <c r="X3">
-        <v>0.1818477236174779</v>
+        <v>0.147171209259801</v>
       </c>
       <c r="Y3">
-        <v>-0.15205934243403</v>
+        <v>-0.3041006654290636</v>
       </c>
       <c r="Z3">
-        <v>0.7953028585820426</v>
+        <v>0.7297070192146098</v>
       </c>
       <c r="AA3">
-        <v>0.01855874574990556</v>
+        <v>-0.03616043919108173</v>
       </c>
       <c r="AB3">
-        <v>0.09881400432582654</v>
+        <v>0.0806115332843247</v>
       </c>
       <c r="AC3">
-        <v>-0.08025525857592099</v>
+        <v>-0.1167719724754064</v>
       </c>
       <c r="AD3">
-        <v>2422.4</v>
+        <v>2613.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2422.4</v>
+        <v>2613.1</v>
       </c>
       <c r="AG3">
-        <v>1689.1</v>
+        <v>1821.7</v>
       </c>
       <c r="AH3">
-        <v>0.6090563950418626</v>
+        <v>0.6326199583595603</v>
       </c>
       <c r="AI3">
-        <v>0.5283545629035072</v>
+        <v>0.5202891048104492</v>
       </c>
       <c r="AJ3">
-        <v>0.5206843403205919</v>
+        <v>0.5455498322951605</v>
       </c>
       <c r="AK3">
-        <v>0.4385564065948332</v>
+        <v>0.4305601512644764</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>119.9</v>
       </c>
       <c r="AM3">
-        <v>-22.3</v>
+        <v>119.9</v>
       </c>
       <c r="AN3">
-        <v>8.074666666666667</v>
+        <v>14.14780725500812</v>
+      </c>
+      <c r="AO3">
+        <v>-1.0767306088407</v>
       </c>
       <c r="AP3">
-        <v>5.630333333333334</v>
+        <v>9.863021115322143</v>
       </c>
       <c r="AQ3">
-        <v>-5.286995515695067</v>
+        <v>-1.0767306088407</v>
       </c>
     </row>
   </sheetData>
